--- a/Learning Path/asset/plan.xlsx
+++ b/Learning Path/asset/plan.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\XIAO\Learning\all_dev_notes\Learning Path\asset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{086ACCA5-BA9E-4DF0-83CA-11C591B6B62D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3BE8778-0C91-44B9-9BA5-4BF26916DE63}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5700" xr2:uid="{1794C119-90C4-43F1-B80C-829B4DF45F9A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17250" windowHeight="5700" xr2:uid="{1794C119-90C4-43F1-B80C-829B4DF45F9A}"/>
   </bookViews>
   <sheets>
     <sheet name="Vue" sheetId="1" r:id="rId1"/>
-    <sheet name="Java" sheetId="2" r:id="rId2"/>
+    <sheet name="健身" sheetId="3" r:id="rId2"/>
+    <sheet name="Java" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>天</t>
   </si>
@@ -38,6 +39,18 @@
   </si>
   <si>
     <t>Udemy Vue Developer 2023</t>
+  </si>
+  <si>
+    <t>prank</t>
+  </si>
+  <si>
+    <t>半俯卧撑</t>
+  </si>
+  <si>
+    <t>俯卧抬腿</t>
+  </si>
+  <si>
+    <t>跑步</t>
   </si>
 </sst>
 </file>
@@ -54,7 +67,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -64,6 +77,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -80,10 +99,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -399,11 +420,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{183C5B76-4190-4C77-8A67-283F826C4677}">
   <dimension ref="A1:AM19"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="47" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="47" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39">
@@ -429,115 +450,115 @@
       <c r="B3" s="1">
         <v>45010</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="4">
         <v>1</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="4">
         <v>2</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="4">
         <v>3</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="4">
         <v>4</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="4">
         <v>5</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="4">
         <v>6</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="4">
         <v>7</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="4">
         <v>8</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="4">
         <v>9</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="4">
         <v>10</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="4">
         <v>11</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="4">
         <v>12</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="4">
         <v>13</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="4">
         <v>14</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="4">
         <v>15</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="4">
         <v>16</v>
       </c>
-      <c r="S3">
+      <c r="S3" s="4">
         <v>17</v>
       </c>
-      <c r="T3">
+      <c r="T3" s="4">
         <v>18</v>
       </c>
-      <c r="U3">
+      <c r="U3" s="4">
         <v>19</v>
       </c>
-      <c r="V3">
+      <c r="V3" s="4">
         <v>20</v>
       </c>
-      <c r="W3">
+      <c r="W3" s="4">
         <v>21</v>
       </c>
-      <c r="X3">
+      <c r="X3" s="4">
         <v>22</v>
       </c>
-      <c r="Y3">
+      <c r="Y3" s="4">
         <v>23</v>
       </c>
-      <c r="Z3">
+      <c r="Z3" s="4">
         <v>24</v>
       </c>
-      <c r="AA3">
+      <c r="AA3" s="4">
         <v>25</v>
       </c>
-      <c r="AB3">
+      <c r="AB3" s="4">
         <v>26</v>
       </c>
-      <c r="AC3">
+      <c r="AC3" s="4">
         <v>27</v>
       </c>
-      <c r="AD3">
+      <c r="AD3" s="4">
         <v>28</v>
       </c>
-      <c r="AE3">
+      <c r="AE3" s="4">
         <v>29</v>
       </c>
-      <c r="AF3">
+      <c r="AF3" s="4">
         <v>30</v>
       </c>
-      <c r="AG3">
+      <c r="AG3" s="4">
         <v>31</v>
       </c>
-      <c r="AH3">
+      <c r="AH3" s="4">
         <v>32</v>
       </c>
-      <c r="AI3">
+      <c r="AI3" s="4">
         <v>33</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ3" s="4">
         <v>34</v>
       </c>
-      <c r="AK3">
+      <c r="AK3" s="4">
         <v>35</v>
       </c>
-      <c r="AL3">
+      <c r="AL3" s="4">
         <v>36</v>
       </c>
-      <c r="AM3">
+      <c r="AM3" s="4">
         <v>37</v>
       </c>
     </row>
@@ -548,106 +569,106 @@
       <c r="B4" s="1">
         <v>45011</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="4">
         <v>38</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="4">
         <v>39</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="4">
         <v>40</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="4">
         <v>41</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="4">
         <v>42</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="4">
         <v>43</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="4">
         <v>44</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="4">
         <v>45</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="4">
         <v>46</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="4">
         <v>47</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="4">
         <v>48</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="4">
         <v>49</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="4">
         <v>50</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="4">
         <v>51</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="4">
         <v>52</v>
       </c>
-      <c r="R4">
+      <c r="R4" s="4">
         <v>53</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="4">
         <v>54</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="4">
         <v>55</v>
       </c>
-      <c r="U4">
+      <c r="U4" s="4">
         <v>56</v>
       </c>
-      <c r="V4">
+      <c r="V4" s="4">
         <v>57</v>
       </c>
-      <c r="W4">
+      <c r="W4" s="4">
         <v>58</v>
       </c>
-      <c r="X4">
+      <c r="X4" s="4">
         <v>59</v>
       </c>
-      <c r="Y4">
+      <c r="Y4" s="4">
         <v>60</v>
       </c>
-      <c r="Z4">
+      <c r="Z4" s="4">
         <v>61</v>
       </c>
-      <c r="AA4">
+      <c r="AA4" s="4">
         <v>62</v>
       </c>
-      <c r="AB4">
+      <c r="AB4" s="4">
         <v>63</v>
       </c>
-      <c r="AC4">
+      <c r="AC4" s="4">
         <v>64</v>
       </c>
-      <c r="AD4">
+      <c r="AD4" s="4">
         <v>65</v>
       </c>
-      <c r="AE4">
+      <c r="AE4" s="4">
         <v>66</v>
       </c>
-      <c r="AF4">
+      <c r="AF4" s="4">
         <v>67</v>
       </c>
-      <c r="AG4">
+      <c r="AG4" s="4">
         <v>68</v>
       </c>
-      <c r="AH4">
+      <c r="AH4" s="4">
         <v>69</v>
       </c>
-      <c r="AI4">
+      <c r="AI4" s="4">
         <v>70</v>
       </c>
-      <c r="AJ4">
+      <c r="AJ4" s="4">
         <v>71</v>
       </c>
     </row>
@@ -658,7 +679,7 @@
       <c r="B5" s="2">
         <v>45012</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="4">
         <v>72</v>
       </c>
       <c r="D5">
@@ -1415,9 +1436,53 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B383F95B-0F0E-4348-837E-206C6A0F4665}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="3">
+        <v>45011</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <v>30</v>
+      </c>
+      <c r="D2">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D1BA9BE-46A6-4A14-B425-181F734A0FD1}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Learning Path/asset/plan.xlsx
+++ b/Learning Path/asset/plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\XIAO\Learning\all_dev_notes\Learning Path\asset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3BE8778-0C91-44B9-9BA5-4BF26916DE63}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44094729-7FAC-4CB3-81F9-E09C3D6660CD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17250" windowHeight="5700" xr2:uid="{1794C119-90C4-43F1-B80C-829B4DF45F9A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5700" xr2:uid="{1794C119-90C4-43F1-B80C-829B4DF45F9A}"/>
   </bookViews>
   <sheets>
     <sheet name="Vue" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>天</t>
   </si>
@@ -51,6 +51,9 @@
   </si>
   <si>
     <t>跑步</t>
+  </si>
+  <si>
+    <t>举手</t>
   </si>
 </sst>
 </file>
@@ -420,11 +423,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{183C5B76-4190-4C77-8A67-283F826C4677}">
   <dimension ref="A1:AM19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="47" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="39" width="4.33203125" customWidth="1"/>
+    <col min="40" max="47" width="3.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39">
@@ -682,13 +686,13 @@
       <c r="C5" s="4">
         <v>72</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="4">
         <v>73</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="4">
         <v>74</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="4">
         <v>75</v>
       </c>
     </row>
@@ -699,19 +703,19 @@
       <c r="B6" s="2">
         <v>45013</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="4">
         <v>76</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="4">
         <v>77</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="4">
         <v>78</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="4">
         <v>79</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="4">
         <v>80</v>
       </c>
     </row>
@@ -1437,13 +1441,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B383F95B-0F0E-4348-837E-206C6A0F4665}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1459,8 +1463,11 @@
       <c r="E1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="3">
         <v>45011</v>
       </c>
@@ -1472,6 +1479,23 @@
       </c>
       <c r="D2">
         <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="3">
+        <v>45012</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>20</v>
+      </c>
+      <c r="D3">
+        <v>60</v>
+      </c>
+      <c r="F3">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1482,7 +1506,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D1BA9BE-46A6-4A14-B425-181F734A0FD1}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Learning Path/asset/plan.xlsx
+++ b/Learning Path/asset/plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\XIAO\Learning\all_dev_notes\Learning Path\asset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44094729-7FAC-4CB3-81F9-E09C3D6660CD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F821BB-58F0-4687-870B-612BFBCC8143}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5700" xr2:uid="{1794C119-90C4-43F1-B80C-829B4DF45F9A}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>天</t>
   </si>
@@ -54,6 +54,12 @@
   </si>
   <si>
     <t>举手</t>
+  </si>
+  <si>
+    <t>重新复习，重做项目</t>
+  </si>
+  <si>
+    <t>俯卧撑</t>
   </si>
 </sst>
 </file>
@@ -1429,7 +1435,15 @@
       </c>
     </row>
     <row r="18" spans="1:39">
-      <c r="B18" s="2"/>
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" s="1">
+        <v>45025</v>
+      </c>
+      <c r="C18" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="19" spans="1:39">
       <c r="B19" s="2"/>
@@ -1441,13 +1455,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B383F95B-0F0E-4348-837E-206C6A0F4665}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1466,8 +1480,11 @@
       <c r="F1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="3">
         <v>45011</v>
       </c>
@@ -1481,7 +1498,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3" s="3">
         <v>45012</v>
       </c>
@@ -1496,6 +1513,31 @@
       </c>
       <c r="F3">
         <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="3">
+        <v>45013</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>60</v>
+      </c>
+      <c r="F4">
+        <v>40</v>
+      </c>
+      <c r="G4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="3">
+        <v>45014</v>
       </c>
     </row>
   </sheetData>

--- a/Learning Path/asset/plan.xlsx
+++ b/Learning Path/asset/plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\XIAO\Learning\all_dev_notes\Learning Path\asset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F821BB-58F0-4687-870B-612BFBCC8143}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B96F2D1A-F572-4F3B-894C-87D0AC8B39F8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5700" xr2:uid="{1794C119-90C4-43F1-B80C-829B4DF45F9A}"/>
   </bookViews>
@@ -732,16 +732,16 @@
       <c r="B7" s="2">
         <v>45014</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="4">
         <v>81</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="4">
         <v>82</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="4">
         <v>83</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="4">
         <v>84</v>
       </c>
     </row>

--- a/Learning Path/asset/plan.xlsx
+++ b/Learning Path/asset/plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\XIAO\Learning\all_dev_notes\Learning Path\asset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B96F2D1A-F572-4F3B-894C-87D0AC8B39F8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4DDE70D-D910-4FFB-B802-047F5521AE23}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5700" xr2:uid="{1794C119-90C4-43F1-B80C-829B4DF45F9A}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>天</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>俯卧撑</t>
+  </si>
+  <si>
+    <t>跳绳</t>
   </si>
 </sst>
 </file>
@@ -752,22 +755,22 @@
       <c r="B8" s="2">
         <v>45015</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="4">
         <v>85</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="4">
         <v>86</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="4">
         <v>87</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="4">
         <v>88</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="4">
         <v>89</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="4">
         <v>90</v>
       </c>
     </row>
@@ -1266,7 +1269,7 @@
       <c r="U16">
         <v>234</v>
       </c>
-      <c r="V16">
+      <c r="V16" s="4">
         <v>235</v>
       </c>
       <c r="W16">
@@ -1328,19 +1331,19 @@
       <c r="D17">
         <v>252</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="4">
         <v>253</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="4">
         <v>254</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="4">
         <v>255</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="4">
         <v>256</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="4">
         <v>257</v>
       </c>
       <c r="J17">
@@ -1370,7 +1373,7 @@
       <c r="R17">
         <v>266</v>
       </c>
-      <c r="S17">
+      <c r="S17" s="4">
         <v>267</v>
       </c>
       <c r="T17">
@@ -1391,31 +1394,31 @@
       <c r="Y17">
         <v>273</v>
       </c>
-      <c r="Z17">
+      <c r="Z17" s="4">
         <v>274</v>
       </c>
-      <c r="AA17">
+      <c r="AA17" s="4">
         <v>275</v>
       </c>
-      <c r="AB17">
+      <c r="AB17" s="4">
         <v>276</v>
       </c>
       <c r="AC17">
         <v>277</v>
       </c>
-      <c r="AD17">
+      <c r="AD17" s="4">
         <v>278</v>
       </c>
-      <c r="AE17">
+      <c r="AE17" s="4">
         <v>279</v>
       </c>
-      <c r="AF17">
+      <c r="AF17" s="4">
         <v>280</v>
       </c>
-      <c r="AG17">
+      <c r="AG17" s="4">
         <v>281</v>
       </c>
-      <c r="AH17">
+      <c r="AH17" s="4">
         <v>282</v>
       </c>
       <c r="AI17">
@@ -1455,13 +1458,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B383F95B-0F0E-4348-837E-206C6A0F4665}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1483,8 +1486,11 @@
       <c r="G1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="3">
         <v>45011</v>
       </c>
@@ -1498,7 +1504,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3" s="3">
         <v>45012</v>
       </c>
@@ -1515,7 +1521,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4" s="3">
         <v>45013</v>
       </c>
@@ -1535,9 +1541,37 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="A5" s="3">
         <v>45014</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>60</v>
+      </c>
+      <c r="F5">
+        <v>60</v>
+      </c>
+      <c r="G5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="3">
+        <v>45015</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="3">
+        <v>45016</v>
       </c>
     </row>
   </sheetData>

--- a/Learning Path/asset/plan.xlsx
+++ b/Learning Path/asset/plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\XIAO\Learning\all_dev_notes\Learning Path\asset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4DDE70D-D910-4FFB-B802-047F5521AE23}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0E3A3B-5E0E-40AB-8430-93756158AADD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5700" xr2:uid="{1794C119-90C4-43F1-B80C-829B4DF45F9A}"/>
   </bookViews>
@@ -781,20 +781,14 @@
       <c r="B9" s="2">
         <v>45016</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="4">
         <v>91</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="4">
         <v>92</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="4">
         <v>93</v>
-      </c>
-      <c r="F9">
-        <v>94</v>
-      </c>
-      <c r="G9">
-        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:39">
@@ -804,109 +798,115 @@
       <c r="B10" s="1">
         <v>45017</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="4">
+        <v>94</v>
+      </c>
+      <c r="D10" s="4">
+        <v>95</v>
+      </c>
+      <c r="E10" s="4">
         <v>96</v>
       </c>
-      <c r="D10">
+      <c r="F10" s="4">
         <v>97</v>
       </c>
-      <c r="E10">
+      <c r="G10" s="4">
         <v>98</v>
       </c>
-      <c r="F10">
+      <c r="H10" s="4">
         <v>99</v>
       </c>
-      <c r="G10">
+      <c r="I10" s="4">
         <v>100</v>
       </c>
-      <c r="H10">
+      <c r="J10" s="4">
         <v>101</v>
       </c>
-      <c r="I10">
+      <c r="K10" s="4">
         <v>102</v>
       </c>
-      <c r="J10">
+      <c r="L10" s="4">
         <v>103</v>
       </c>
-      <c r="K10">
+      <c r="M10" s="4">
         <v>104</v>
       </c>
-      <c r="L10">
+      <c r="N10" s="4">
         <v>105</v>
       </c>
-      <c r="M10">
+      <c r="O10" s="4">
         <v>106</v>
       </c>
-      <c r="N10">
+      <c r="P10" s="4">
         <v>107</v>
       </c>
-      <c r="O10">
+      <c r="Q10" s="4">
         <v>108</v>
       </c>
-      <c r="P10">
+      <c r="R10" s="4">
         <v>109</v>
       </c>
-      <c r="Q10">
+      <c r="S10" s="4">
         <v>110</v>
       </c>
-      <c r="R10">
+      <c r="T10" s="4">
         <v>111</v>
       </c>
-      <c r="S10">
+      <c r="U10" s="4">
         <v>112</v>
       </c>
-      <c r="T10">
+      <c r="V10" s="4">
         <v>113</v>
       </c>
-      <c r="U10">
+      <c r="W10" s="4">
         <v>114</v>
       </c>
-      <c r="V10">
+      <c r="X10" s="4">
         <v>115</v>
       </c>
-      <c r="W10">
+      <c r="Y10" s="4">
         <v>116</v>
       </c>
-      <c r="X10">
+      <c r="Z10" s="4">
         <v>117</v>
       </c>
-      <c r="Y10">
+      <c r="AA10" s="4">
         <v>118</v>
       </c>
-      <c r="Z10">
+      <c r="AB10" s="4">
         <v>119</v>
       </c>
-      <c r="AA10">
+      <c r="AC10" s="4">
         <v>120</v>
       </c>
-      <c r="AB10">
+      <c r="AD10" s="4">
         <v>121</v>
       </c>
-      <c r="AC10">
+      <c r="AE10" s="4">
         <v>122</v>
       </c>
-      <c r="AD10">
+      <c r="AF10">
         <v>123</v>
       </c>
-      <c r="AE10">
+      <c r="AG10">
         <v>124</v>
       </c>
-      <c r="AF10">
+      <c r="AH10">
         <v>125</v>
       </c>
-      <c r="AG10">
+      <c r="AI10">
         <v>126</v>
       </c>
-      <c r="AH10">
+      <c r="AJ10">
         <v>127</v>
       </c>
-      <c r="AI10">
+      <c r="AK10">
         <v>128</v>
       </c>
-      <c r="AJ10">
+      <c r="AL10">
         <v>129</v>
       </c>
-      <c r="AK10">
+      <c r="AM10">
         <v>130</v>
       </c>
     </row>
@@ -1091,6 +1091,9 @@
       <c r="G14">
         <v>180</v>
       </c>
+      <c r="H14">
+        <v>181</v>
+      </c>
     </row>
     <row r="15" spans="1:39">
       <c r="A15">
@@ -1100,109 +1103,109 @@
         <v>45022</v>
       </c>
       <c r="C15">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D15">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E15">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F15">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G15">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H15">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I15">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J15">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K15">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L15">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M15">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N15">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O15">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P15">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q15">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="R15">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="S15">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="T15">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="U15">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="V15">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="W15">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="X15">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Y15">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Z15">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AA15">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AB15">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AC15">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AD15">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AE15">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AF15">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG15">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AH15">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AI15">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AJ15">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AK15">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="1:39">
@@ -1213,108 +1216,105 @@
         <v>45023</v>
       </c>
       <c r="C16">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D16">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E16">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F16">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G16">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H16">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I16">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J16">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K16">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L16">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M16">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N16">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O16">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P16">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q16">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="R16">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="S16">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="T16">
-        <v>233</v>
-      </c>
-      <c r="U16">
         <v>234</v>
       </c>
-      <c r="V16" s="4">
+      <c r="U16" s="4">
         <v>235</v>
       </c>
+      <c r="V16">
+        <v>236</v>
+      </c>
       <c r="W16">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="X16">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Y16">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Z16">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AA16">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AB16">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AC16">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AD16">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AE16">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AF16">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG16">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AH16">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AI16">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AJ16">
-        <v>249</v>
-      </c>
-      <c r="AK16">
         <v>250</v>
       </c>
     </row>

--- a/Learning Path/asset/plan.xlsx
+++ b/Learning Path/asset/plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\XIAO\Learning\all_dev_notes\Learning Path\asset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0E3A3B-5E0E-40AB-8430-93756158AADD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4DB045-9323-4788-9FC5-8EE3AF4BEBC9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5700" xr2:uid="{1794C119-90C4-43F1-B80C-829B4DF45F9A}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>天</t>
   </si>
@@ -54,9 +54,6 @@
   </si>
   <si>
     <t>举手</t>
-  </si>
-  <si>
-    <t>重新复习，重做项目</t>
   </si>
   <si>
     <t>俯卧撑</t>
@@ -885,30 +882,6 @@
       <c r="AE10" s="4">
         <v>122</v>
       </c>
-      <c r="AF10">
-        <v>123</v>
-      </c>
-      <c r="AG10">
-        <v>124</v>
-      </c>
-      <c r="AH10">
-        <v>125</v>
-      </c>
-      <c r="AI10">
-        <v>126</v>
-      </c>
-      <c r="AJ10">
-        <v>127</v>
-      </c>
-      <c r="AK10">
-        <v>128</v>
-      </c>
-      <c r="AL10">
-        <v>129</v>
-      </c>
-      <c r="AM10">
-        <v>130</v>
-      </c>
     </row>
     <row r="11" spans="1:39">
       <c r="A11">
@@ -917,110 +890,107 @@
       <c r="B11" s="1">
         <v>45018</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="4">
+        <v>123</v>
+      </c>
+      <c r="D11" s="4">
+        <v>124</v>
+      </c>
+      <c r="E11" s="4">
+        <v>125</v>
+      </c>
+      <c r="F11" s="4">
+        <v>126</v>
+      </c>
+      <c r="G11" s="4">
+        <v>127</v>
+      </c>
+      <c r="H11" s="4">
+        <v>128</v>
+      </c>
+      <c r="I11" s="4">
+        <v>129</v>
+      </c>
+      <c r="J11" s="4">
+        <v>130</v>
+      </c>
+      <c r="K11" s="4">
         <v>131</v>
       </c>
-      <c r="D11">
+      <c r="L11" s="4">
         <v>132</v>
       </c>
-      <c r="E11">
+      <c r="M11" s="4">
         <v>133</v>
       </c>
-      <c r="F11">
+      <c r="N11" s="4">
         <v>134</v>
       </c>
-      <c r="G11">
+      <c r="O11" s="4">
         <v>135</v>
       </c>
-      <c r="H11">
+      <c r="P11" s="4">
         <v>136</v>
       </c>
-      <c r="I11">
+      <c r="Q11" s="4">
         <v>137</v>
       </c>
-      <c r="J11">
+      <c r="R11" s="4">
         <v>138</v>
       </c>
-      <c r="K11">
+      <c r="S11" s="4">
         <v>139</v>
       </c>
-      <c r="L11">
+      <c r="T11" s="4">
         <v>140</v>
       </c>
-      <c r="M11">
+      <c r="U11" s="4">
         <v>141</v>
       </c>
-      <c r="N11">
+      <c r="V11" s="4">
         <v>142</v>
       </c>
-      <c r="O11">
+      <c r="W11" s="4">
         <v>143</v>
       </c>
-      <c r="P11">
+      <c r="X11" s="4">
         <v>144</v>
       </c>
-      <c r="Q11">
+      <c r="Y11" s="4">
         <v>145</v>
       </c>
-      <c r="R11">
+      <c r="Z11" s="4">
         <v>146</v>
       </c>
-      <c r="S11">
+      <c r="AA11" s="4">
         <v>147</v>
       </c>
-      <c r="T11">
+      <c r="AB11" s="4">
         <v>148</v>
       </c>
-      <c r="U11">
+      <c r="AC11" s="4">
         <v>149</v>
       </c>
-      <c r="V11">
+      <c r="AD11" s="4">
         <v>150</v>
       </c>
-      <c r="W11">
+      <c r="AE11" s="4">
         <v>151</v>
       </c>
-      <c r="X11">
+      <c r="AF11" s="4">
         <v>152</v>
       </c>
-      <c r="Y11">
+      <c r="AG11" s="4">
         <v>153</v>
       </c>
-      <c r="Z11">
+      <c r="AH11" s="4">
         <v>154</v>
       </c>
-      <c r="AA11">
+      <c r="AI11" s="4">
         <v>155</v>
       </c>
-      <c r="AB11">
+      <c r="AJ11" s="4">
         <v>156</v>
-      </c>
-      <c r="AC11">
-        <v>157</v>
-      </c>
-      <c r="AD11">
-        <v>158</v>
-      </c>
-      <c r="AE11">
-        <v>159</v>
-      </c>
-      <c r="AF11">
-        <v>160</v>
-      </c>
-      <c r="AG11">
-        <v>161</v>
-      </c>
-      <c r="AH11">
-        <v>162</v>
-      </c>
-      <c r="AI11">
-        <v>163</v>
-      </c>
-      <c r="AJ11">
-        <v>164</v>
-      </c>
-      <c r="AK11">
-        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:39">
@@ -1031,19 +1001,31 @@
         <v>45019</v>
       </c>
       <c r="C12">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="D12">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="E12">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="F12">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="G12">
-        <v>170</v>
+        <v>161</v>
+      </c>
+      <c r="H12">
+        <v>162</v>
+      </c>
+      <c r="I12">
+        <v>163</v>
+      </c>
+      <c r="J12">
+        <v>164</v>
+      </c>
+      <c r="K12">
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:39">
@@ -1054,19 +1036,19 @@
         <v>45020</v>
       </c>
       <c r="C13">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D13">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E13">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F13">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G13">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:39">
@@ -1077,22 +1059,19 @@
         <v>45021</v>
       </c>
       <c r="C14">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D14">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E14">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F14">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G14">
-        <v>180</v>
-      </c>
-      <c r="H14">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:39">
@@ -1103,109 +1082,22 @@
         <v>45022</v>
       </c>
       <c r="C15">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D15">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="E15">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="F15">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="G15">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="H15">
-        <v>187</v>
-      </c>
-      <c r="I15">
-        <v>188</v>
-      </c>
-      <c r="J15">
-        <v>189</v>
-      </c>
-      <c r="K15">
-        <v>190</v>
-      </c>
-      <c r="L15">
-        <v>191</v>
-      </c>
-      <c r="M15">
-        <v>192</v>
-      </c>
-      <c r="N15">
-        <v>193</v>
-      </c>
-      <c r="O15">
-        <v>194</v>
-      </c>
-      <c r="P15">
-        <v>195</v>
-      </c>
-      <c r="Q15">
-        <v>196</v>
-      </c>
-      <c r="R15">
-        <v>197</v>
-      </c>
-      <c r="S15">
-        <v>198</v>
-      </c>
-      <c r="T15">
-        <v>199</v>
-      </c>
-      <c r="U15">
-        <v>200</v>
-      </c>
-      <c r="V15">
-        <v>201</v>
-      </c>
-      <c r="W15">
-        <v>202</v>
-      </c>
-      <c r="X15">
-        <v>203</v>
-      </c>
-      <c r="Y15">
-        <v>204</v>
-      </c>
-      <c r="Z15">
-        <v>205</v>
-      </c>
-      <c r="AA15">
-        <v>206</v>
-      </c>
-      <c r="AB15">
-        <v>207</v>
-      </c>
-      <c r="AC15">
-        <v>208</v>
-      </c>
-      <c r="AD15">
-        <v>209</v>
-      </c>
-      <c r="AE15">
-        <v>210</v>
-      </c>
-      <c r="AF15">
-        <v>211</v>
-      </c>
-      <c r="AG15">
-        <v>212</v>
-      </c>
-      <c r="AH15">
-        <v>213</v>
-      </c>
-      <c r="AI15">
-        <v>214</v>
-      </c>
-      <c r="AJ15">
-        <v>215</v>
-      </c>
-      <c r="AK15">
-        <v>216</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:39">
@@ -1216,106 +1108,109 @@
         <v>45023</v>
       </c>
       <c r="C16">
-        <v>217</v>
+        <v>182</v>
       </c>
       <c r="D16">
-        <v>218</v>
+        <v>183</v>
       </c>
       <c r="E16">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="F16">
-        <v>220</v>
+        <v>185</v>
       </c>
       <c r="G16">
-        <v>221</v>
+        <v>186</v>
       </c>
       <c r="H16">
-        <v>222</v>
+        <v>187</v>
       </c>
       <c r="I16">
-        <v>223</v>
+        <v>188</v>
       </c>
       <c r="J16">
-        <v>224</v>
+        <v>189</v>
       </c>
       <c r="K16">
-        <v>225</v>
+        <v>190</v>
       </c>
       <c r="L16">
-        <v>226</v>
+        <v>191</v>
       </c>
       <c r="M16">
-        <v>227</v>
+        <v>192</v>
       </c>
       <c r="N16">
-        <v>228</v>
+        <v>193</v>
       </c>
       <c r="O16">
-        <v>229</v>
+        <v>194</v>
       </c>
       <c r="P16">
-        <v>230</v>
+        <v>195</v>
       </c>
       <c r="Q16">
-        <v>231</v>
+        <v>196</v>
       </c>
       <c r="R16">
-        <v>232</v>
+        <v>197</v>
       </c>
       <c r="S16">
-        <v>233</v>
+        <v>198</v>
       </c>
       <c r="T16">
-        <v>234</v>
-      </c>
-      <c r="U16" s="4">
-        <v>235</v>
+        <v>199</v>
+      </c>
+      <c r="U16">
+        <v>200</v>
       </c>
       <c r="V16">
-        <v>236</v>
+        <v>201</v>
       </c>
       <c r="W16">
-        <v>237</v>
+        <v>202</v>
       </c>
       <c r="X16">
-        <v>238</v>
+        <v>203</v>
       </c>
       <c r="Y16">
-        <v>239</v>
+        <v>204</v>
       </c>
       <c r="Z16">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="AA16">
-        <v>241</v>
+        <v>206</v>
       </c>
       <c r="AB16">
-        <v>242</v>
+        <v>207</v>
       </c>
       <c r="AC16">
-        <v>243</v>
+        <v>208</v>
       </c>
       <c r="AD16">
-        <v>244</v>
+        <v>209</v>
       </c>
       <c r="AE16">
-        <v>245</v>
+        <v>210</v>
       </c>
       <c r="AF16">
-        <v>246</v>
+        <v>211</v>
       </c>
       <c r="AG16">
-        <v>247</v>
+        <v>212</v>
       </c>
       <c r="AH16">
-        <v>248</v>
+        <v>213</v>
       </c>
       <c r="AI16">
-        <v>249</v>
+        <v>214</v>
       </c>
       <c r="AJ16">
-        <v>250</v>
+        <v>215</v>
+      </c>
+      <c r="AK16">
+        <v>216</v>
       </c>
     </row>
     <row r="17" spans="1:39">
@@ -1326,115 +1221,106 @@
         <v>45024</v>
       </c>
       <c r="C17">
-        <v>251</v>
+        <v>217</v>
       </c>
       <c r="D17">
-        <v>252</v>
-      </c>
-      <c r="E17" s="4">
-        <v>253</v>
-      </c>
-      <c r="F17" s="4">
-        <v>254</v>
-      </c>
-      <c r="G17" s="4">
-        <v>255</v>
-      </c>
-      <c r="H17" s="4">
-        <v>256</v>
-      </c>
-      <c r="I17" s="4">
-        <v>257</v>
+        <v>218</v>
+      </c>
+      <c r="E17">
+        <v>219</v>
+      </c>
+      <c r="F17">
+        <v>220</v>
+      </c>
+      <c r="G17">
+        <v>221</v>
+      </c>
+      <c r="H17">
+        <v>222</v>
+      </c>
+      <c r="I17">
+        <v>223</v>
       </c>
       <c r="J17">
-        <v>258</v>
+        <v>224</v>
       </c>
       <c r="K17">
-        <v>259</v>
+        <v>225</v>
       </c>
       <c r="L17">
-        <v>260</v>
+        <v>226</v>
       </c>
       <c r="M17">
-        <v>261</v>
+        <v>227</v>
       </c>
       <c r="N17">
-        <v>262</v>
+        <v>228</v>
       </c>
       <c r="O17">
-        <v>263</v>
+        <v>229</v>
       </c>
       <c r="P17">
-        <v>264</v>
+        <v>230</v>
       </c>
       <c r="Q17">
-        <v>265</v>
+        <v>231</v>
       </c>
       <c r="R17">
-        <v>266</v>
-      </c>
-      <c r="S17" s="4">
-        <v>267</v>
+        <v>232</v>
+      </c>
+      <c r="S17">
+        <v>233</v>
       </c>
       <c r="T17">
-        <v>268</v>
-      </c>
-      <c r="U17">
-        <v>269</v>
+        <v>234</v>
+      </c>
+      <c r="U17" s="4">
+        <v>235</v>
       </c>
       <c r="V17">
-        <v>270</v>
+        <v>236</v>
       </c>
       <c r="W17">
-        <v>271</v>
+        <v>237</v>
       </c>
       <c r="X17">
-        <v>272</v>
+        <v>238</v>
       </c>
       <c r="Y17">
-        <v>273</v>
-      </c>
-      <c r="Z17" s="4">
-        <v>274</v>
-      </c>
-      <c r="AA17" s="4">
-        <v>275</v>
-      </c>
-      <c r="AB17" s="4">
-        <v>276</v>
+        <v>239</v>
+      </c>
+      <c r="Z17">
+        <v>240</v>
+      </c>
+      <c r="AA17">
+        <v>241</v>
+      </c>
+      <c r="AB17">
+        <v>242</v>
       </c>
       <c r="AC17">
-        <v>277</v>
-      </c>
-      <c r="AD17" s="4">
-        <v>278</v>
-      </c>
-      <c r="AE17" s="4">
-        <v>279</v>
-      </c>
-      <c r="AF17" s="4">
-        <v>280</v>
-      </c>
-      <c r="AG17" s="4">
-        <v>281</v>
-      </c>
-      <c r="AH17" s="4">
-        <v>282</v>
+        <v>243</v>
+      </c>
+      <c r="AD17">
+        <v>244</v>
+      </c>
+      <c r="AE17">
+        <v>245</v>
+      </c>
+      <c r="AF17">
+        <v>246</v>
+      </c>
+      <c r="AG17">
+        <v>247</v>
+      </c>
+      <c r="AH17">
+        <v>248</v>
       </c>
       <c r="AI17">
-        <v>283</v>
+        <v>249</v>
       </c>
       <c r="AJ17">
-        <v>284</v>
-      </c>
-      <c r="AK17">
-        <v>285</v>
-      </c>
-      <c r="AL17">
-        <v>286</v>
-      </c>
-      <c r="AM17">
-        <v>287</v>
+        <v>250</v>
       </c>
     </row>
     <row r="18" spans="1:39">
@@ -1444,8 +1330,116 @@
       <c r="B18" s="1">
         <v>45025</v>
       </c>
-      <c r="C18" t="s">
-        <v>9</v>
+      <c r="C18">
+        <v>251</v>
+      </c>
+      <c r="D18">
+        <v>252</v>
+      </c>
+      <c r="E18" s="4">
+        <v>253</v>
+      </c>
+      <c r="F18" s="4">
+        <v>254</v>
+      </c>
+      <c r="G18" s="4">
+        <v>255</v>
+      </c>
+      <c r="H18" s="4">
+        <v>256</v>
+      </c>
+      <c r="I18" s="4">
+        <v>257</v>
+      </c>
+      <c r="J18">
+        <v>258</v>
+      </c>
+      <c r="K18">
+        <v>259</v>
+      </c>
+      <c r="L18">
+        <v>260</v>
+      </c>
+      <c r="M18">
+        <v>261</v>
+      </c>
+      <c r="N18">
+        <v>262</v>
+      </c>
+      <c r="O18">
+        <v>263</v>
+      </c>
+      <c r="P18">
+        <v>264</v>
+      </c>
+      <c r="Q18">
+        <v>265</v>
+      </c>
+      <c r="R18">
+        <v>266</v>
+      </c>
+      <c r="S18" s="4">
+        <v>267</v>
+      </c>
+      <c r="T18">
+        <v>268</v>
+      </c>
+      <c r="U18">
+        <v>269</v>
+      </c>
+      <c r="V18">
+        <v>270</v>
+      </c>
+      <c r="W18">
+        <v>271</v>
+      </c>
+      <c r="X18">
+        <v>272</v>
+      </c>
+      <c r="Y18">
+        <v>273</v>
+      </c>
+      <c r="Z18" s="4">
+        <v>274</v>
+      </c>
+      <c r="AA18" s="4">
+        <v>275</v>
+      </c>
+      <c r="AB18" s="4">
+        <v>276</v>
+      </c>
+      <c r="AC18">
+        <v>277</v>
+      </c>
+      <c r="AD18" s="4">
+        <v>278</v>
+      </c>
+      <c r="AE18" s="4">
+        <v>279</v>
+      </c>
+      <c r="AF18" s="4">
+        <v>280</v>
+      </c>
+      <c r="AG18" s="4">
+        <v>281</v>
+      </c>
+      <c r="AH18" s="4">
+        <v>282</v>
+      </c>
+      <c r="AI18" s="4">
+        <v>283</v>
+      </c>
+      <c r="AJ18" s="4">
+        <v>284</v>
+      </c>
+      <c r="AK18">
+        <v>285</v>
+      </c>
+      <c r="AL18">
+        <v>286</v>
+      </c>
+      <c r="AM18">
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:39">
@@ -1484,10 +1478,10 @@
         <v>8</v>
       </c>
       <c r="G1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" t="s">
         <v>10</v>
-      </c>
-      <c r="H1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:8">

--- a/Learning Path/asset/plan.xlsx
+++ b/Learning Path/asset/plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\XIAO\Learning\all_dev_notes\Learning Path\asset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4DB045-9323-4788-9FC5-8EE3AF4BEBC9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E5F28C-B1A8-430A-AA70-1F313F772728}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5700" xr2:uid="{1794C119-90C4-43F1-B80C-829B4DF45F9A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5700" activeTab="1" xr2:uid="{1794C119-90C4-43F1-B80C-829B4DF45F9A}"/>
   </bookViews>
   <sheets>
     <sheet name="Vue" sheetId="1" r:id="rId1"/>
@@ -1452,7 +1452,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B383F95B-0F0E-4348-837E-206C6A0F4665}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
@@ -1566,6 +1566,54 @@
     <row r="7" spans="1:8">
       <c r="A7" s="3">
         <v>45016</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="3">
+        <v>45017</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="3">
+        <v>45018</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="3">
+        <v>45019</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="3">
+        <v>45020</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="3">
+        <v>45021</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="3">
+        <v>45022</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="3">
+        <v>45023</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="3">
+        <v>45024</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="3">
+        <v>45025</v>
+      </c>
+      <c r="D16">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/Learning Path/asset/plan.xlsx
+++ b/Learning Path/asset/plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\XIAO\Learning\all_dev_notes\Learning Path\asset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E5F28C-B1A8-430A-AA70-1F313F772728}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89184699-5CAB-42FF-A766-977B2CBD19A6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5700" activeTab="1" xr2:uid="{1794C119-90C4-43F1-B80C-829B4DF45F9A}"/>
   </bookViews>
@@ -1612,8 +1612,17 @@
       <c r="A16" s="3">
         <v>45025</v>
       </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>18</v>
+      </c>
       <c r="D16">
         <v>60</v>
+      </c>
+      <c r="G16">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
